--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T07:36:35+00:00</t>
+    <t>2026-06-22T13:39:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:39:21+00:00</t>
+    <t>2026-07-22T12:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:47:59+00:00</t>
+    <t>2026-07-22T12:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:55:33+00:00</t>
+    <t>2026-07-23T09:09:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:09:32+00:00</t>
+    <t>2026-07-31T15:05:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-bp-method.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T15:05:17+00:00</t>
+    <t>2026-08-03T08:32:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
